--- a/markdown_generator/courses.xlsx
+++ b/markdown_generator/courses.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29A9818-8FF8-0049-B8BD-FAD276C9C9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4007E604-94A8-564B-926A-284351247636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$6</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>title</t>
   </si>
@@ -40,6 +43,9 @@
     <t>location</t>
   </si>
   <si>
+    <t>course_url</t>
+  </si>
+  <si>
     <t>notes</t>
   </si>
   <si>
@@ -97,20 +103,29 @@
     <t>01/01/2025</t>
   </si>
   <si>
-    <t>My role is to design, develop the course and co-teach it with Prof.dr. Koen Hindriks.</t>
-  </si>
-  <si>
     <t>2026-01-pca</t>
   </si>
   <si>
     <t>01/01/2026</t>
+  </si>
+  <si>
+    <t>https://socialrobotics.atlassian.net/wiki/spaces/PCA21/pages/3117779057/Home+-+PCA+2026+Overview</t>
+  </si>
+  <si>
+    <t>My role is a coordinator and teacher to design, develop the course and teach it.</t>
+  </si>
+  <si>
+    <t>https://socialrobotics.atlassian.net/wiki/spaces/PCA2/overview</t>
+  </si>
+  <si>
+    <t>My role is a teacher to design, develop the course and co-teach it with Prof.dr. Koen Hindriks.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,16 +136,40 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F4F8F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3FA"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -143,30 +182,41 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -467,19 +517,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="19.5" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="37.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="21.33203125" customWidth="1"/>
-    <col min="7" max="7" width="88.33203125" customWidth="1"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
+    <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,125 +550,141 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
+    <row r="5" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="G5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="6" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
+      <c r="F6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="H6" r:id="rId1" xr:uid="{E3A9CC00-81F4-2D41-9245-E9B5200589ED}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/markdown_generator/courses.xlsx
+++ b/markdown_generator/courses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4007E604-94A8-564B-926A-284351247636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD846D0-9859-504F-8696-DF48570D74DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
   <si>
     <t>title</t>
   </si>
@@ -58,9 +58,6 @@
     <t>2018-09-ir0</t>
   </si>
   <si>
-    <t>University of Amsterdam, Informatics Institute</t>
-  </si>
-  <si>
     <t>01/09/2018</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>2025-01-pca</t>
   </si>
   <si>
-    <t>Vrije Universiteit Amsterdam, Faculty of Science</t>
-  </si>
-  <si>
     <t>01/01/2025</t>
   </si>
   <si>
@@ -119,6 +113,21 @@
   </si>
   <si>
     <t>My role is a teacher to design, develop the course and co-teach it with Prof.dr. Koen Hindriks.</t>
+  </si>
+  <si>
+    <t>University of Amsterdam</t>
+  </si>
+  <si>
+    <t>Vrije Universiteit Amsterdam</t>
+  </si>
+  <si>
+    <t>2027-02-ca</t>
+  </si>
+  <si>
+    <t>Conversational Agents (XB_0182)</t>
+  </si>
+  <si>
+    <t>01/02/2027</t>
   </si>
 </sst>
 </file>
@@ -200,7 +209,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -212,6 +221,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -517,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -527,7 +539,7 @@
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
-    <col min="8" max="8" width="35" customWidth="1"/>
+    <col min="8" max="8" width="81.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -567,40 +579,40 @@
         <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="F3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="H3" s="3"/>
     </row>
@@ -612,73 +624,97 @@
         <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="C6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="H7" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/markdown_generator/courses.xlsx
+++ b/markdown_generator/courses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD846D0-9859-504F-8696-DF48570D74DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0683ABC7-52AB-794F-AC2C-B399B9990E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
   <si>
     <t>title</t>
   </si>
@@ -31,33 +31,45 @@
     <t>type</t>
   </si>
   <si>
+    <t>role</t>
+  </si>
+  <si>
     <t>url_slug</t>
   </si>
   <si>
     <t>venue</t>
   </si>
   <si>
-    <t>date</t>
+    <t>startdate</t>
+  </si>
+  <si>
+    <t>enddate</t>
   </si>
   <si>
     <t>location</t>
   </si>
   <si>
+    <t>notes</t>
+  </si>
+  <si>
     <t>course_url</t>
   </si>
   <si>
-    <t>notes</t>
-  </si>
-  <si>
     <t>Information Retrieval (Zoekmachines)</t>
   </si>
   <si>
     <t>Bachelor Course</t>
   </si>
   <si>
+    <t>Teacher</t>
+  </si>
+  <si>
     <t>2018-09-ir0</t>
   </si>
   <si>
+    <t>University of Amsterdam</t>
+  </si>
+  <si>
     <t>01/09/2018</t>
   </si>
   <si>
@@ -94,47 +106,59 @@
     <t>2025-01-pca</t>
   </si>
   <si>
+    <t>Vrije Universiteit Amsterdam</t>
+  </si>
+  <si>
     <t>01/01/2025</t>
   </si>
   <si>
+    <t>My role is a teacher to design, develop the course and co-teach it with Prof.dr. Koen Hindriks.</t>
+  </si>
+  <si>
+    <t>https://socialrobotics.atlassian.net/wiki/spaces/PCA2/overview</t>
+  </si>
+  <si>
     <t>2026-01-pca</t>
   </si>
   <si>
     <t>01/01/2026</t>
   </si>
   <si>
+    <t>My role is a coordinator and teacher to design, develop the course and teach it.</t>
+  </si>
+  <si>
     <t>https://socialrobotics.atlassian.net/wiki/spaces/PCA21/pages/3117779057/Home+-+PCA+2026+Overview</t>
   </si>
   <si>
-    <t>My role is a coordinator and teacher to design, develop the course and teach it.</t>
-  </si>
-  <si>
-    <t>https://socialrobotics.atlassian.net/wiki/spaces/PCA2/overview</t>
-  </si>
-  <si>
-    <t>My role is a teacher to design, develop the course and co-teach it with Prof.dr. Koen Hindriks.</t>
-  </si>
-  <si>
-    <t>University of Amsterdam</t>
-  </si>
-  <si>
-    <t>Vrije Universiteit Amsterdam</t>
+    <t>Conversational Agents (XB_0182)</t>
   </si>
   <si>
     <t>2027-02-ca</t>
   </si>
   <si>
-    <t>Conversational Agents (XB_0182)</t>
-  </si>
-  <si>
     <t>01/02/2027</t>
+  </si>
+  <si>
+    <t>Teaching Assisant</t>
+  </si>
+  <si>
+    <t>Coordinator, Teacher</t>
+  </si>
+  <si>
+    <t>26/03/2027</t>
+  </si>
+  <si>
+    <t>28/02/2026</t>
+  </si>
+  <si>
+    <t>28/02/2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,14 +177,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -205,11 +221,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -220,15 +235,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -529,20 +537,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="7" max="7" width="60" customWidth="1"/>
-    <col min="8" max="8" width="81.1640625" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="45" customWidth="1"/>
+    <col min="6" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="89.83203125" customWidth="1"/>
+    <col min="10" max="10" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,165 +570,198 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="C7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="F7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="4"/>
+      <c r="J7" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <hyperlinks>
-    <hyperlink ref="H6" r:id="rId1" xr:uid="{E3A9CC00-81F4-2D41-9245-E9B5200589ED}"/>
-  </hyperlinks>
+  <autoFilter ref="A1:J7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/markdown_generator/courses.xlsx
+++ b/markdown_generator/courses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0683ABC7-52AB-794F-AC2C-B399B9990E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810467F7-0138-E149-BDEC-1664CA7474A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
   <si>
     <t>title</t>
   </si>
@@ -139,9 +139,6 @@
     <t>01/02/2027</t>
   </si>
   <si>
-    <t>Teaching Assisant</t>
-  </si>
-  <si>
     <t>Coordinator, Teacher</t>
   </si>
   <si>
@@ -152,6 +149,18 @@
   </si>
   <si>
     <t>28/02/2025</t>
+  </si>
+  <si>
+    <t>TA</t>
+  </si>
+  <si>
+    <t>01/10/2018</t>
+  </si>
+  <si>
+    <t>01/12/2018</t>
+  </si>
+  <si>
+    <t>01/10/2020</t>
   </si>
 </sst>
 </file>
@@ -224,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -233,6 +242,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -590,7 +602,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>13</v>
@@ -601,7 +613,9 @@
       <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="H2" s="3" t="s">
         <v>16</v>
       </c>
@@ -618,7 +632,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>20</v>
@@ -629,7 +643,9 @@
       <c r="F3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
       </c>
@@ -646,7 +662,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>22</v>
@@ -657,7 +673,9 @@
       <c r="F4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="H4" s="3" t="s">
         <v>16</v>
       </c>
@@ -686,7 +704,7 @@
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -706,7 +724,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>31</v>
@@ -718,7 +736,7 @@
         <v>32</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>16</v>
@@ -738,7 +756,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>36</v>
@@ -750,7 +768,7 @@
         <v>37</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>16</v>

--- a/markdown_generator/courses.xlsx
+++ b/markdown_generator/courses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810467F7-0138-E149-BDEC-1664CA7474A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D14E015-34BF-0F49-81D3-6EB9579C686D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
   <si>
     <t>title</t>
   </si>
@@ -161,6 +161,9 @@
   </si>
   <si>
     <t>01/10/2020</t>
+  </si>
+  <si>
+    <t>My role is a coordinator and teacher to design, develop the course and teach it with Prof.dr. Koen Hindriks.</t>
   </si>
 </sst>
 </file>
@@ -774,7 +777,7 @@
         <v>16</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="J7" s="2"/>
     </row>
